--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:56:04+00:00</t>
+    <t>2026-10-15T09:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:21:11+00:00</t>
+    <t>2026-10-15T12:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:03:42+00:00</t>
+    <t>2026-10-15T12:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:49:20+00:00</t>
+    <t>2026-10-15T13:32:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:32:05+00:00</t>
+    <t>2026-10-15T13:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:47:34+00:00</t>
+    <t>2026-10-15T13:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:54:27+00:00</t>
+    <t>2026-10-15T14:04:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
+++ b/branches/feature-careteam/StructureDefinition-contact-via-team.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T14:04:45+00:00</t>
+    <t>2026-10-28T12:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
